--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487838_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487838_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2559</v>
+        <v>4.1594</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4774</v>
+        <v>6.2927</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.2214</v>
+        <v>-2.1334</v>
       </c>
       <c r="G2" t="n">
         <v>3.0951</v>
@@ -610,13 +610,13 @@
         <v>2.2893</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.2554</v>
+        <v>-1.3519</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.4354</v>
+        <v>-0.62</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.82</v>
+        <v>-0.7319</v>
       </c>
       <c r="V2" t="n">
         <v>1.1675</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. DJERY</t>
+          <t>J. KNOTEK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2394</v>
+        <v>2.2242</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2072</v>
+        <v>2.7657</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0322</v>
+        <v>-0.5415</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4419</v>
+        <v>0.5291</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4354</v>
+        <v>3.2192</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0065</v>
+        <v>-2.6901</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8259</v>
+        <v>1.4846</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7867</v>
+        <v>3.4318</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0392</v>
+        <v>-1.9472</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.384</v>
+        <v>-0.9555</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3513</v>
+        <v>-0.2126</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0326</v>
+        <v>-0.7429</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2081</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2487</v>
+        <v>2.4974</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6518</v>
+        <v>-1.6431</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2544</v>
+        <v>-0.7272</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3974</v>
+        <v>-0.9159</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9376</v>
+        <v>3.9625</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1675</v>
+        <v>5.13</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.23</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. KNOTEK</t>
+          <t>J. DJERY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2159</v>
+        <v>1.1435</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9923</v>
+        <v>0.5224</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7764</v>
+        <v>0.6211</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5291</v>
+        <v>0.4419</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2192</v>
+        <v>0.4354</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.6901</v>
+        <v>0.0065</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4846</v>
+        <v>0.8259</v>
       </c>
       <c r="K4" t="n">
-        <v>3.4318</v>
+        <v>0.7867</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.9472</v>
+        <v>0.0392</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9555</v>
+        <v>-0.384</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2126</v>
+        <v>-0.3513</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7429</v>
+        <v>-0.0326</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6244</v>
+        <v>0.2081</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.1218</v>
+        <v>-1.0406</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4974</v>
+        <v>1.2487</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.6514</v>
+        <v>-0.4441</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.5006</v>
+        <v>-0.4305</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.1508</v>
+        <v>-0.0136</v>
       </c>
       <c r="V4" t="n">
-        <v>3.9625</v>
+        <v>0.9376</v>
       </c>
       <c r="W4" t="n">
-        <v>5.13</v>
+        <v>1.1675</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1675</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.374</v>
+        <v>-0.3447</v>
       </c>
       <c r="E5" t="n">
         <v>0.0392</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4132</v>
+        <v>-0.3838</v>
       </c>
       <c r="G5" t="n">
         <v>-0.3936</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0196</v>
+        <v>0.0489</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0196</v>
+        <v>0.0489</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7574</v>
+        <v>-0.6041</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2378</v>
+        <v>-0.1726</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5196</v>
+        <v>-0.4315</v>
       </c>
       <c r="G6" t="n">
         <v>1.6343</v>
@@ -922,13 +922,13 @@
         <v>1.2487</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1618</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1272</v>
+        <v>0.1924</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.289</v>
+        <v>-0.2009</v>
       </c>
       <c r="V6" t="n">
         <v>-1.3975</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8122</v>
+        <v>-2.4589</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2737</v>
+        <v>-0.7442</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.5385</v>
+        <v>-1.7147</v>
       </c>
       <c r="G7" t="n">
         <v>-2.4277</v>
@@ -1000,13 +1000,13 @@
         <v>1.4568</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4293</v>
+        <v>-0.2174</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7111</v>
+        <v>0.2405</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2818</v>
+        <v>-0.4579</v>
       </c>
       <c r="V7" t="n">
         <v>-0.23</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.2223</v>
+        <v>-3.0499</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.529</v>
+        <v>-2.3566</v>
       </c>
       <c r="F8" t="n">
         <v>-0.6933</v>
@@ -1078,10 +1078,10 @@
         <v>1.8731</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.053</v>
+        <v>-0.8806</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.46</v>
+        <v>-0.2876</v>
       </c>
       <c r="U8" t="n">
         <v>-0.593</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.8563</v>
+        <v>-3.4299</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.2718</v>
+        <v>-3.9922</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4155</v>
+        <v>0.5623</v>
       </c>
       <c r="G9" t="n">
         <v>-2.7707</v>
@@ -1156,13 +1156,13 @@
         <v>0.8325</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8774999999999999</v>
+        <v>-0.4511</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.3076</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2903</v>
+        <v>-0.1435</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.2988</v>
+        <v>-5.597</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9626</v>
+        <v>-3.2607</v>
       </c>
       <c r="F10" t="n">
         <v>-2.3362</v>
@@ -1234,10 +1234,10 @@
         <v>2.0812</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1835</v>
+        <v>-1.4816</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2023</v>
+        <v>-0.5004999999999999</v>
       </c>
       <c r="U10" t="n">
         <v>-0.9811</v>
@@ -1267,16 +1267,16 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.6098</v>
+        <v>-7.957400000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.558799999999999</v>
+        <v>-0.9063000000000008</v>
       </c>
       <c r="F11" t="n">
-        <v>-7.0509</v>
+        <v>-7.051</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.6539</v>
+        <v>-3.653899999999999</v>
       </c>
       <c r="H11" t="n">
         <v>-1.6945</v>
@@ -1312,16 +1312,16 @@
         <v>13.5277</v>
       </c>
       <c r="S11" t="n">
-        <v>-7.081900000000001</v>
+        <v>-6.4294</v>
       </c>
       <c r="T11" t="n">
-        <v>-3.0928</v>
+        <v>-2.4405</v>
       </c>
       <c r="U11" t="n">
-        <v>-3.989</v>
+        <v>-3.9889</v>
       </c>
       <c r="V11" t="n">
-        <v>3.166500000000001</v>
+        <v>3.1665</v>
       </c>
       <c r="W11" t="n">
         <v>9.446300000000001</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.7582</v>
+        <v>5.5876</v>
       </c>
       <c r="E12" t="n">
-        <v>3.2817</v>
+        <v>3.8175</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4764</v>
+        <v>1.77</v>
       </c>
       <c r="G12" t="n">
         <v>2.2802</v>
@@ -1390,13 +1390,13 @@
         <v>2.0812</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8977000000000001</v>
+        <v>-0.0683</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5096000000000001</v>
+        <v>0.0262</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3882</v>
+        <v>-0.0946</v>
       </c>
       <c r="V12" t="n">
         <v>2.3351</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. DIENE</t>
+          <t>J. PARDINA MOLINA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.0889</v>
+        <v>4.0106</v>
       </c>
       <c r="E13" t="n">
-        <v>4.7826</v>
+        <v>3.5593</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6937</v>
+        <v>0.4513</v>
       </c>
       <c r="G13" t="n">
-        <v>2.1847</v>
+        <v>1.3956</v>
       </c>
       <c r="H13" t="n">
-        <v>2.4133</v>
+        <v>1.0642</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2286</v>
+        <v>0.3315</v>
       </c>
       <c r="J13" t="n">
-        <v>3.8668</v>
+        <v>1.2489</v>
       </c>
       <c r="K13" t="n">
-        <v>3.6709</v>
+        <v>1.1705</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1959</v>
+        <v>0.0784</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.6821</v>
+        <v>0.1468</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.2576</v>
+        <v>-0.1063</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4245</v>
+        <v>0.2531</v>
       </c>
       <c r="P13" t="n">
-        <v>0.4162</v>
+        <v>1.8731</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4568</v>
+        <v>1.8731</v>
       </c>
       <c r="S13" t="n">
-        <v>2.3017</v>
+        <v>1.0957</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3726</v>
+        <v>0.913</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9291</v>
+        <v>0.1827</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.8137</v>
+        <v>-0.3538</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5838</v>
+        <v>1.3975</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.3975</v>
+        <v>-1.7513</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. PARDINA MOLINA</t>
+          <t>P. DIENE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.0781</v>
+        <v>2.8309</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7737</v>
+        <v>3.8182</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3045</v>
+        <v>-0.9873</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3956</v>
+        <v>2.1847</v>
       </c>
       <c r="H14" t="n">
-        <v>1.0642</v>
+        <v>2.4133</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3315</v>
+        <v>-0.2286</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2489</v>
+        <v>3.8668</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1705</v>
+        <v>3.6709</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0784</v>
+        <v>0.1959</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1468</v>
+        <v>-1.6821</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1063</v>
+        <v>-1.2576</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2531</v>
+        <v>-0.4245</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8731</v>
+        <v>0.4162</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8731</v>
+        <v>1.4568</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1632</v>
+        <v>1.0437</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1273</v>
+        <v>0.4082</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0359</v>
+        <v>0.6355</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3538</v>
+        <v>-0.8137</v>
       </c>
       <c r="W14" t="n">
-        <v>1.3975</v>
+        <v>0.5838</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.7513</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8719</v>
+        <v>1.928</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7772</v>
+        <v>1.5984</v>
       </c>
       <c r="F15" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.3296</v>
       </c>
       <c r="G15" t="n">
         <v>0.0873</v>
@@ -1624,13 +1624,13 @@
         <v>0.8325</v>
       </c>
       <c r="S15" t="n">
-        <v>2.0759</v>
+        <v>1.1321</v>
       </c>
       <c r="T15" t="n">
-        <v>2.0746</v>
+        <v>0.8959</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0013</v>
+        <v>0.2362</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1238</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8817</v>
+        <v>1.0524</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3276</v>
+        <v>-0.2082</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5541</v>
+        <v>1.2605</v>
       </c>
       <c r="G16" t="n">
         <v>1.1516</v>
@@ -1702,13 +1702,13 @@
         <v>0.6244</v>
       </c>
       <c r="S16" t="n">
-        <v>1.7302</v>
+        <v>0.9008</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3106</v>
+        <v>0.7749</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4195</v>
+        <v>0.1259</v>
       </c>
       <c r="V16" t="n">
         <v>-0.5838</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8738</v>
+        <v>1.0015</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6502</v>
+        <v>1.543</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7764</v>
+        <v>-0.5416</v>
       </c>
       <c r="G17" t="n">
         <v>-0.6181</v>
@@ -1780,13 +1780,13 @@
         <v>1.0406</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1325</v>
+        <v>-0.0047</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1866</v>
+        <v>-0.2938</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0542</v>
+        <v>0.2891</v>
       </c>
       <c r="V17" t="n">
         <v>0.5838</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7715</v>
+        <v>-0.7627</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.2812</v>
+        <v>-2.0668</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5097</v>
+        <v>1.3041</v>
       </c>
       <c r="G18" t="n">
         <v>-1.5074</v>
@@ -1858,13 +1858,13 @@
         <v>2.2893</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5278</v>
+        <v>0.5366</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0091</v>
+        <v>0.2234</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5187</v>
+        <v>0.3132</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3732</v>
+        <v>-1.1064</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.9884</v>
+        <v>-1.8097</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6152</v>
+        <v>0.7032</v>
       </c>
       <c r="G19" t="n">
         <v>0.1897</v>
@@ -1936,13 +1936,13 @@
         <v>1.0406</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2518</v>
+        <v>1.015</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3791</v>
+        <v>0.7996</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1273</v>
+        <v>0.2153</v>
       </c>
       <c r="V19" t="n">
         <v>-0.23</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4156</v>
+        <v>-2.1132</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.117</v>
+        <v>0.0974</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.2986</v>
+        <v>-2.2106</v>
       </c>
       <c r="G20" t="n">
         <v>0.5406</v>
@@ -2014,13 +2014,13 @@
         <v>1.4568</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9407</v>
+        <v>1.2431</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2668</v>
+        <v>0.4811</v>
       </c>
       <c r="U20" t="n">
-        <v>0.674</v>
+        <v>0.7621</v>
       </c>
       <c r="V20" t="n">
         <v>-3.2726</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.3825</v>
+        <v>-3.8188</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.1555</v>
+        <v>-3.2982</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.227</v>
+        <v>-0.5206</v>
       </c>
       <c r="G21" t="n">
         <v>-2.0504</v>
@@ -2092,13 +2092,13 @@
         <v>1.8731</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3758</v>
+        <v>0.1879</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0967</v>
+        <v>-0.2395</v>
       </c>
       <c r="U21" t="n">
-        <v>0.721</v>
+        <v>0.4274</v>
       </c>
       <c r="V21" t="n">
         <v>-0.7076</v>
@@ -2125,16 +2125,16 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>8.6098</v>
+        <v>8.609900000000003</v>
       </c>
       <c r="E22" t="n">
         <v>7.050899999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5589</v>
+        <v>1.5586</v>
       </c>
       <c r="G22" t="n">
-        <v>3.6538</v>
+        <v>3.653799999999999</v>
       </c>
       <c r="H22" t="n">
         <v>1.6946</v>
@@ -2170,10 +2170,10 @@
         <v>14.5684</v>
       </c>
       <c r="S22" t="n">
-        <v>7.0817</v>
+        <v>7.0819</v>
       </c>
       <c r="T22" t="n">
-        <v>3.989</v>
+        <v>3.988999999999999</v>
       </c>
       <c r="U22" t="n">
         <v>3.0928</v>
